--- a/pipeline/credit_rating/output/visrating_xhtn_20261029.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261029.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -526,12 +526,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -541,33 +541,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tích cực</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>THCL12602</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-gelex-group-26102026.188.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-thcl12602-29102026.189.html</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-gelex-group-26102026.188.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-thcl12602-29102026.189.html</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -577,33 +581,33 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46321</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -618,29 +622,33 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tích cực</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-abbank-21102026.187.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-gelex-group-26102026.188.html</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-abbank-21102026.187.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-gelex-group-26102026.188.html</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -650,28 +658,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco Auto</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -698,22 +706,22 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tasco-auto-20102026.186.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-abbank-21102026.187.html</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-tasco-auto-20102026.186.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-abbank-21102026.187.html</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -723,11 +731,11 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="5">
@@ -738,18 +746,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VPBank</t>
+          <t>Công ty Cổ phần Tasco Auto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Thay đổi triển vọng</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -764,33 +772,29 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Tích cực</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-vpbanks-20102026.185.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tasco-auto-20102026.186.html</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-vpbanks-20102026.185.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-tasco-auto-20102026.186.html</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -800,7 +804,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -810,28 +814,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Chứng khoán VPBank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Thay đổi triển vọng</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -841,37 +845,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>BCML12602</t>
-        </is>
-      </c>
+          <t>Tích cực</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-bcml12602-19102026.184.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-vpbanks-20102026.185.html</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-bcml12602-19102026.184.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-vpbanks-20102026.185.html</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -881,22 +881,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tổng Công ty Dầu Việt Nam - Công ty Cổ phần</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -930,17 +930,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BCML12602</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-bcml12602-19102026.184.html</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-bcml12602-19102026.184.html</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-dau-viet-nam-cong-ty-co-phan.38.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -950,22 +962,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Bất động sản Thế Kỷ</t>
+          <t>Tổng Công ty Dầu Việt Nam - Công ty Cổ phần</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -976,12 +988,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -991,7 +1003,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -999,29 +1011,17 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>CREL12601</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-crel12601-09102026.182.html</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-crel12601-09102026.182.html</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-bat-dong-san-the-ky.52.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-dau-viet-nam-cong-ty-co-phan.38.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1031,11 +1031,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="9">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1080,15 +1080,19 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CREL12601</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-cen-land-09102026.181.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-crel12601-09102026.182.html</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-cen-land-09102026.181.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-crel12601-09102026.182.html</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1108,7 +1112,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1118,23 +1122,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
+          <t>Công ty Cổ phần Bất động sản Thế Kỷ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1149,7 +1153,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1160,22 +1164,22 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-shs-02102026.180.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-cen-land-09102026.181.html</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-shs-02102026.180.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-cen-land-09102026.181.html</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-bat-dong-san-the-ky.52.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1185,11 +1189,11 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="11">
@@ -1200,7 +1204,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tổng Công ty Cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
+          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1211,7 +1215,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1226,7 +1230,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1235,16 +1239,24 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-shs-02102026.180.html</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-shs-02102026.180.html</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1254,7 +1266,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1264,23 +1276,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
+          <t>Tổng Công ty Cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1295,29 +1307,25 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-cap-treo-ba-na-25092026.178.html</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-ba-na-service-cable-car-25092026.178.html</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1327,22 +1335,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Cơ khí Công nghệ Cao Siba</t>
+          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1353,12 +1361,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1368,37 +1376,29 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>SBG426001</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-sbg426001-21092026.177.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-cap-treo-ba-na-25092026.178.html</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-sbg426001-21092026.177.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-ba-na-service-cable-car-25092026.178.html</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-co-khi-cong-nghe-cao-siba.51.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1408,11 +1408,11 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="14">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1457,15 +1457,19 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SBG426001</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-siba-high-tech-21092026.176.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-sbg426001-21092026.177.html</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-siba-high-tech-21092026.176.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-sbg426001-21092026.177.html</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1495,12 +1499,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Công ty Cổ phần Tập đoàn Cơ khí Công nghệ Cao Siba</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1511,7 +1515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1526,7 +1530,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1537,22 +1541,22 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202609_phenikaa_rating_announcement_vn.175.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-siba-high-tech-21092026.176.html</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202609_phenikaa_rating_announcement_en.175.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-siba-high-tech-21092026.176.html</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-co-khi-cong-nghe-cao-siba.51.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1562,33 +1566,33 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán LPS</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1603,7 +1607,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1612,16 +1616,24 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202609_phenikaa_rating_announcement_vn.175.html</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202609_phenikaa_rating_announcement_en.175.html</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1631,22 +1643,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
+          <t>Công ty Cổ phần Chứng khoán LPS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1657,7 +1669,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1672,7 +1684,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1681,24 +1693,16 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tps-04092026.173.html</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-tps-04092026.173.html</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1708,38 +1712,38 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
+          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1757,29 +1761,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>THCL12601</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-26082026.172.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tps-04092026.173.html</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-26082026.172.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-tps-04092026.173.html</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1789,22 +1789,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1840,27 +1840,27 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BCML12601</t>
+          <t>THCL12601</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-bcm12601-24072026.171.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-26082026.172.html</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-bcm12601-24072026.171.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-26082026.172.html</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1870,11 +1870,11 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46227</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="20">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1919,15 +1919,19 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BCML12601</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-becamex-24072026.170.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-bcm12601-24072026.171.html</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-becamex-24072026.170.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-bcm12601-24072026.171.html</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1947,7 +1951,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -1957,12 +1961,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Container Việt Nam</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1973,12 +1977,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1996,29 +2000,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>VSCL12601</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-23072026.169.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-becamex-24072026.170.html</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-23072026.169.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-becamex-24072026.170.html</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-container-viet-nam.50.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="22">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2077,15 +2077,19 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>VSCL12601</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-viconship-23072026.168.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-23072026.169.html</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-viconship-23072026.168.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-23072026.169.html</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2115,23 +2119,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán AIS</t>
+          <t>Công ty Cổ phần Container Việt Nam</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2146,7 +2150,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2157,22 +2161,22 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-chung-khoan-ais-01072026.167.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-viconship-23072026.168.html</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-ais-securities-01072026.167.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-viconship-23072026.168.html</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-container-viet-nam.50.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>50</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2182,38 +2186,38 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46204</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
+          <t>Công ty Cổ phần Chứng khoán AIS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2223,7 +2227,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2231,29 +2235,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>STA12601</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-24062026.165.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-chung-khoan-ais-01072026.167.html</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-24062026.165.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-ais-securities-01072026.167.html</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46197</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="25">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Nước Aqua One</t>
+          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2314,19 +2314,27 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AQ112501</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>STA12601</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-24062026.165.html</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-24062026.165.html</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2336,7 +2344,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2367,7 +2375,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2385,7 +2393,11 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>AQ112501</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
@@ -2405,7 +2417,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2420,7 +2432,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
+          <t>Công ty Cổ phần Nước Aqua One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -2446,7 +2458,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2459,12 +2471,12 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2474,7 +2486,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2484,12 +2496,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2500,7 +2512,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2515,7 +2527,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2524,24 +2536,16 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-starbay-23062026.159.html</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-starbay-23062026.159.html</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2551,11 +2555,11 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="29">
@@ -2566,7 +2570,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần VinaLiving Holdings</t>
+          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2592,7 +2596,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2601,16 +2605,24 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-starbay-23062026.159.html</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-starbay-23062026.159.html</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2620,7 +2632,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2630,18 +2642,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán BIDV</t>
+          <t>Công ty Cổ phần VinaLiving Holdings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2661,7 +2673,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2674,12 +2686,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2689,38 +2701,38 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46190</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Công ty TNHH Greenland Phố Hoa</t>
+          <t>Công ty Cổ phần Chứng khoán BIDV</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2730,7 +2742,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2738,29 +2750,17 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>GPH12601</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-16062026.156.html</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-16062026.156.html</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-greenland-pho-hoa.48.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2770,11 +2770,11 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="32">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2819,15 +2819,19 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>GPH12601</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-greenland-pho-hoa-16062026.155.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-16062026.156.html</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-greenland-pho-hoa-16062026.155.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-16062026.156.html</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2847,7 +2851,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2862,18 +2866,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
+          <t>Công ty TNHH Greenland Phố Hoa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2888,7 +2892,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2897,16 +2901,24 @@
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-greenland-pho-hoa-16062026.155.html</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-greenland-pho-hoa-16062026.155.html</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-greenland-pho-hoa.48.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2916,7 +2928,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2926,12 +2938,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
+          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2942,7 +2954,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2957,29 +2969,25 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-mcredit-11062026.153.html</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-mcredit-11062026.153.html</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2989,33 +2997,33 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần TNG Land</t>
+          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3030,33 +3038,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BBB</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tng-land-10062026.152.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-mcredit-11062026.153.html</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-tng-land-10062026.152.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-mcredit-11062026.153.html</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tng-land.47.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3066,22 +3070,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
+          <t>Công ty Cổ phần TNG Land</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -3092,7 +3096,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3116,16 +3120,24 @@
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tng-land-10062026.152.html</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-tng-land-10062026.152.html</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tng-land.47.html</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3135,22 +3147,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46178</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -3189,12 +3201,12 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3204,28 +3216,28 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VPBank</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3245,7 +3257,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3258,12 +3270,12 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3273,33 +3285,33 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46174</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Vận tải Dầu khí Thái Bình Dương</t>
+          <t>Công ty Cổ phần Chứng khoán VPBank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3323,24 +3335,16 @@
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvtrans-pacific-25052026.146.html</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-pvtrans-pacific-25052026.146.html</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-van-tai-dau-khi-thai-binh-duong.43.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3350,33 +3354,33 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46167</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Vận tải Dầu khí Thái Bình Dương</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3391,7 +3395,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3402,22 +3406,22 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_tpb_rating_announcement_vn.137.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvtrans-pacific-25052026.146.html</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_tpb_rating_announcement_en.137.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-pvtrans-pacific-25052026.146.html</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-van-tai-dau-khi-thai-binh-duong.43.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3427,17 +3431,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46164</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3453,7 +3457,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3477,8 +3481,16 @@
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_tpb_rating_announcement_vn.137.html</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202605_tpb_rating_announcement_en.137.html</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
@@ -3496,22 +3508,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -3522,7 +3534,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3537,29 +3549,25 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-ocb-15052026.138.html</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-ocb-15052026.138.html</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3569,11 +3577,11 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="43">
@@ -3584,18 +3592,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần FECON</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3610,33 +3618,29 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BBB-</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_rating_annoucement_vn.118.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-ocb-15052026.138.html</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_FECON_rating_annoucement_en.118.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-ocb-15052026.138.html</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-fecon.45.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3646,7 +3650,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3656,23 +3660,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
+          <t>Công ty Cổ phần FECON</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3687,7 +3691,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3698,22 +3702,22 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_VND_rating_announcement_vn.80.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_rating_annoucement_vn.118.html</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_VND_rating_announcement_en.80.html</t>
+          <t>https://visrating.com/rating-results/report/202605_FECON_rating_annoucement_en.118.html</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-fecon.45.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3723,38 +3727,38 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần FECON</t>
+          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3764,7 +3768,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3772,29 +3776,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>FCN12601</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_bond_rating_announcement_vn.135.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_VND_rating_announcement_vn.80.html</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_FECON_bond_rating_announcement_en.135.html</t>
+          <t>https://visrating.com/rating-results/report/202605_VND_rating_announcement_en.80.html</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-fecon.45.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3804,11 +3804,11 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="46">
@@ -3819,23 +3819,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán MB</t>
+          <t>Công ty Cổ phần FECON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3853,25 +3853,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>FCN12601</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_bond_rating_announcement_vn.135.html</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
+          <t>https://visrating.com/rating-results/report/202605_FECON_bond_rating_announcement_en.135.html</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-fecon.45.html</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3881,7 +3885,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3891,12 +3895,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán UP</t>
+          <t>Công ty Cổ phần Chứng khoán MB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3907,7 +3911,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3922,29 +3926,33 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_ups_rating_announcement_vn.84.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_ups_rating_announcement_en.84.html</t>
+          <t>https://visrating.com/rating-results/report/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3954,22 +3962,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Công ty Cổ phần Chứng khoán UP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3980,7 +3988,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3995,33 +4003,29 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_lpb_rating_announcement_vn-pdf.48.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_ups_rating_announcement_vn.84.html</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_lpb_rating_announcement_en-pdf.48.html</t>
+          <t>https://visrating.com/rating-results/report/202605_ups_rating_announcement_en.84.html</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4031,33 +4035,33 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4072,25 +4076,33 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tích cực</t>
+          <t>Ổn định</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_lpb_rating_announcement_vn-pdf.48.html</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202605_lpb_rating_announcement_en-pdf.48.html</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4100,33 +4112,33 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46136</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4141,29 +4153,25 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Tích cực</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4173,11 +4181,11 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="51">
@@ -4204,7 +4212,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4218,19 +4226,15 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>VABCLH2330001</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.112.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.112.html</t>
+          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4250,7 +4254,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4297,17 +4301,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>VABCLH2431001</t>
+          <t>VABCLH2330001</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.111.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.112.html</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.111.html</t>
+          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.112.html</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4327,7 +4331,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4337,28 +4341,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco Auto</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4368,25 +4372,33 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BBB+</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>VABCLH2431001</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.111.html</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.111.html</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4396,11 +4408,11 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="54">
@@ -4411,13 +4423,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Công ty Cổ phần Tasco Auto</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4437,7 +4449,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4450,12 +4462,12 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4465,7 +4477,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4475,23 +4487,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tổng Công ty Dầu Việt Nam - Công ty Cổ phần</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4506,7 +4518,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4515,24 +4527,16 @@
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvoil-16042026-SDq.119.html</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-pvoil-16042026-yDJ.119.html</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-dau-viet-nam-cong-ty-co-phan.38.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4542,22 +4546,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
+          <t>Tổng Công ty Dầu Việt Nam - Công ty Cổ phần</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -4568,7 +4572,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4583,7 +4587,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4592,16 +4596,24 @@
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvoil-16042026-SDq.119.html</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-pvoil-16042026-yDJ.119.html</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-dau-viet-nam-cong-ty-co-phan.38.html</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4611,33 +4623,33 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
+          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nâng bậc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4661,24 +4673,16 @@
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/tps-bao-cao-ket-qua-xep-hang-tin-nhiem-20260408.114.html</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/tps-rating-announcement-20260408.114.html</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4688,22 +4692,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tổng Công ty Cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
+          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -4714,7 +4718,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Nâng bậc</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4738,16 +4742,24 @@
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/tps-bao-cao-ket-qua-xep-hang-tin-nhiem-20260408.114.html</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/tps-rating-announcement-20260408.114.html</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4757,22 +4769,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46115</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
+          <t>Tổng Công ty Cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -4798,7 +4810,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4811,12 +4823,12 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4826,28 +4838,28 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4880,12 +4892,12 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4895,33 +4907,33 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46107</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán LPS</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4936,7 +4948,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4945,24 +4957,16 @@
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202603-lpbs-bao-cao-xhtn-pdf.109.html</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202603-lpbs-rating-announcement-pdf.109.html</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4972,33 +4976,33 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46094</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Chứng khoán LPS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5013,7 +5017,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5022,16 +5026,24 @@
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202603-lpbs-bao-cao-xhtn-pdf.109.html</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202603-lpbs-rating-announcement-pdf.109.html</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5041,38 +5053,38 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46052</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5082,33 +5094,25 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>VABLH2431002</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-tp-ket-thuc-xh-07012026-pdf.107.html</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-withdrawal-07012026-pdf.107.html</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5118,38 +5122,38 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46029</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Thay đổi triển vọng</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5159,33 +5163,33 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Tích cực</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>VABLH2431002</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260106_gex_rating-announcement_vn-pdf.131.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-tp-ket-thuc-xh-07012026-pdf.107.html</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20260106_gex_rating-announcement_en-pdf.131.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-withdrawal-07012026-pdf.107.html</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5195,33 +5199,33 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>31/12/2025</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán AIS</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Thay đổi triển vọng</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5236,25 +5240,33 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Ổn định</t>
+          <t>Tích cực</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260106_gex_rating-announcement_vn-pdf.131.html</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/20260106_gex_rating-announcement_en-pdf.131.html</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5264,38 +5276,38 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46022</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>24/12/2025</t>
+          <t>31/12/2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Nước Aqua One</t>
+          <t>Công ty Cổ phần Chứng khoán AIS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5305,7 +5317,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5313,29 +5325,17 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>AQ112501</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_bond_rating_announcement_vn.143.html</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/20251224_aquaone_bond_rating_announcement_en.143.html</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5345,11 +5345,11 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="67">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
+          <t>Công ty Cổ phần Nước Aqua One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5394,25 +5394,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>AQ112501</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_thaco_rating_announcement_vn-pdf.100.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_bond_rating_announcement_vn.143.html</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20251224_thaco_rating_announcement_en-pdf.100.html</t>
+          <t>https://visrating.com/rating-results/report/20251224_aquaone_bond_rating_announcement_en.143.html</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5422,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Nước Aqua One</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -5463,7 +5467,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5474,22 +5478,22 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_rating_announcement_vn-pdf.98.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_thaco_rating_announcement_vn-pdf.100.html</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20251224_aquaone_rating_announcement_en-pdf.98.html</t>
+          <t>https://visrating.com/rating-results/report/20251224_thaco_rating_announcement_en-pdf.100.html</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5499,7 +5503,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5509,12 +5513,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>24/12/2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần VinaLiving Holdings</t>
+          <t>Công ty Cổ phần Nước Aqua One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -5551,22 +5555,22 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_vinaliving_rating_announcement_vn-pdf.97.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_rating_announcement_vn-pdf.98.html</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/2025_vinaliving_rating_announcement_en-pdf.97.html</t>
+          <t>https://visrating.com/rating-results/report/20251224_aquaone_rating_announcement_en-pdf.98.html</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5576,28 +5580,28 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán BIDV</t>
+          <t>Công ty Cổ phần VinaLiving Holdings</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5628,22 +5632,22 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512-bsi-bao-cao-xhtn-pdf.93.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_vinaliving_rating_announcement_vn-pdf.97.html</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202512-bsi-rating-announcement-pdf.93.html</t>
+          <t>https://visrating.com/rating-results/report/2025_vinaliving_rating_announcement_en-pdf.97.html</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5653,22 +5657,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
+          <t>Công ty Cổ phần Chứng khoán BIDV</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -5694,7 +5698,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5705,22 +5709,22 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-tvs-bao-cao-kqxhtn-16122025vn-pdf.92.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512-bsi-bao-cao-xhtn-pdf.93.html</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-tvs-rating-announcement-16122025en-pdf.92.html</t>
+          <t>https://visrating.com/rating-results/report/202512-bsi-rating-announcement-pdf.93.html</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5730,22 +5734,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -5756,12 +5760,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5771,7 +5775,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5779,21 +5783,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>VABLH2431002</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-tvs-bao-cao-kqxhtn-16122025vn-pdf.92.html</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/visrating-tvs-rating-announcement-16122025en-pdf.92.html</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5803,11 +5811,11 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
     </row>
     <row r="73">
@@ -5854,7 +5862,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>VABCLH2330001</t>
+          <t>VABLH2431002</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5876,7 +5884,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5891,7 +5899,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -5907,7 +5915,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5917,7 +5925,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5925,17 +5933,21 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>VABCLH2330001</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5945,7 +5957,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5960,7 +5972,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -5976,7 +5988,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5986,7 +5998,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5994,21 +6006,17 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>VABCLH2431001</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6018,7 +6026,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6028,28 +6036,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6067,25 +6075,21 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512_hut_rating_announcement_vn-pdf.91.html</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202512_hut_rating_announcement_en-pdf.91.html</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>VABCLH2431001</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6095,17 +6099,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6121,7 +6125,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6145,8 +6149,16 @@
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512_hut_rating_announcement_vn-pdf.91.html</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202512_hut_rating_announcement_en-pdf.91.html</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
@@ -6164,11 +6176,11 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="78">
@@ -6179,7 +6191,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -6190,7 +6202,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6214,24 +6226,16 @@
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_sgr_rating_announcement_vn-pdf.89.html</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/2025_sgr_rating_announcement_en-pdf.89.html</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6241,7 +6245,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6251,18 +6255,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VPBank</t>
+          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6282,7 +6286,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6293,22 +6297,22 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202511-rating-announcement-vpbanks-vn-pdf.88.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_sgr_rating_announcement_vn-pdf.89.html</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202511-rating-announcement-vpbanks-en-pdf.88.html</t>
+          <t>https://visrating.com/rating-results/report/2025_sgr_rating_announcement_en-pdf.89.html</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6318,22 +6322,22 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Chứng khoán VPBank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -6344,7 +6348,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6359,7 +6363,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6368,16 +6372,24 @@
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202511-rating-announcement-vpbanks-vn-pdf.88.html</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202511-rating-announcement-vpbanks-en-pdf.88.html</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6387,22 +6399,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>45982</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -6428,7 +6440,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6441,12 +6453,12 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6456,11 +6468,11 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>45975</v>
+        <v>45982</v>
       </c>
     </row>
     <row r="82">
@@ -6471,7 +6483,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán UP</t>
+          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -6497,7 +6509,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6510,12 +6522,12 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6525,7 +6537,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6540,7 +6552,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán MB</t>
+          <t>Công ty Cổ phần Chứng khoán UP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -6566,7 +6578,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6579,12 +6591,12 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6594,7 +6606,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6609,7 +6621,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Chứng khoán MB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -6648,12 +6660,12 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6663,7 +6675,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6673,12 +6685,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -6717,12 +6729,12 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6732,28 +6744,28 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>45969</v>
+        <v>45975</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6773,7 +6785,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6786,12 +6798,12 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6801,33 +6813,33 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>45954</v>
+        <v>45969</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6842,7 +6854,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6851,24 +6863,16 @@
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251022_abb_rating_announcement_vn-pdf.78.html</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/20251022_abb_rating_announcement_en-pdf.78.html</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6878,11 +6882,11 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="88">
@@ -6893,7 +6897,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -6904,7 +6908,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6928,16 +6932,24 @@
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251022_abb_rating_announcement_vn-pdf.78.html</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/20251022_abb_rating_announcement_en-pdf.78.html</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6947,7 +6959,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -6957,23 +6969,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco Auto</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6988,7 +7000,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6997,24 +7009,16 @@
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/251020_tasco-auto_rating_announcement_vn-pdf.76.html</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202510_tasco-auto_rating_announcement_en-pdf.76.html</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7024,28 +7028,28 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tổng Công ty Cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
+          <t>Công ty Cổ phần Tasco Auto</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7065,7 +7069,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7076,22 +7080,22 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_vbi_bao_cao_ket_qua_xhtn_03102025-pdf.66.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/251020_tasco-auto_rating_announcement_vn-pdf.76.html</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating_vbi_rating_announcement_03102025-pdf.66.html</t>
+          <t>https://visrating.com/rating-results/report/202510_tasco-auto_rating_announcement_en-pdf.76.html</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7101,22 +7105,22 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>45933</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
+          <t>Tổng Công ty Cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -7142,7 +7146,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7153,22 +7157,22 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251002-shs-bao-cao-xhtn-pdf.65.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_vbi_bao_cao_ket_qua_xhtn_03102025-pdf.66.html</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20251002-shs-rating-announcement-en-pdf.65.html</t>
+          <t>https://visrating.com/rating-results/report/visrating_vbi_rating_announcement_03102025-pdf.66.html</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7178,28 +7182,28 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
+          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7219,7 +7223,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7230,22 +7234,22 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250926_bnc_rating_announcement_vn-pdf.64.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251002-shs-bao-cao-xhtn-pdf.65.html</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250926_bnc_rating_announcement_en-pdf.64.html</t>
+          <t>https://visrating.com/rating-results/report/20251002-shs-rating-announcement-en-pdf.65.html</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7255,22 +7259,22 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -7281,7 +7285,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7296,7 +7300,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7307,22 +7311,22 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202509_phenikaa_rating_announcement_vn-pdf.63.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250926_bnc_rating_announcement_vn-pdf.64.html</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202509_phenikaa_rating_announcement_en-pdf.63.html</t>
+          <t>https://visrating.com/rating-results/report/20250926_bnc_rating_announcement_en-pdf.64.html</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7332,33 +7336,33 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7373,7 +7377,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7384,22 +7388,22 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250905-tps-bao-cao-xhtn-pdf.62.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202509_phenikaa_rating_announcement_vn-pdf.63.html</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250905-tps-rating-announcement-pdf.62.html</t>
+          <t>https://visrating.com/rating-results/report/202509_phenikaa_rating_announcement_en-pdf.63.html</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7409,28 +7413,28 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>45905</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7450,7 +7454,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7461,22 +7465,22 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250801_bcm_rating_announcement_vn-pdf.61.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250905-tps-bao-cao-xhtn-pdf.62.html</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250801_bcm_rating_announcement_en-pdf.61.html</t>
+          <t>https://visrating.com/rating-results/report/20250905-tps-rating-announcement-pdf.62.html</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7486,28 +7490,28 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>45870</v>
+        <v>45905</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán AIS</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7527,7 +7531,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7538,22 +7542,22 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250701_ais_rating_announcement_vn-pdf.59.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250801_bcm_rating_announcement_vn-pdf.61.html</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250701_ais_rating_announcement_en-pdf.59.html</t>
+          <t>https://visrating.com/rating-results/report/20250801_bcm_rating_announcement_en-pdf.61.html</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7563,22 +7567,22 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Chứng khoán AIS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -7594,7 +7598,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7604,7 +7608,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7612,29 +7616,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>VABCLH2330001</t>
-        </is>
-      </c>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.145.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250701_ais_rating_announcement_vn-pdf.59.html</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.145.html</t>
+          <t>https://visrating.com/rating-results/report/20250701_ais_rating_announcement_en-pdf.59.html</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7644,11 +7644,11 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>45820</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="98">
@@ -7695,17 +7695,17 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>VABCLH2431001</t>
+          <t>VABCLH2330001</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.144.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.145.html</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.144.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.145.html</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7776,17 +7776,17 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>VABLH2431002</t>
+          <t>VABCLH2431001</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.58.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.144.html</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.58.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.144.html</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7855,25 +7855,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>VABLH2431002</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250612-rating-announcement-mcredit-vn-pdf.55.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.58.html</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250612-rating-announcement-mcredit-en-pdf.55.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.58.html</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7883,7 +7887,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7893,23 +7897,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>04/06/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7924,7 +7928,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7933,16 +7937,24 @@
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250612-rating-announcement-mcredit-vn-pdf.55.html</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/20250612-rating-announcement-mcredit-en-pdf.55.html</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7952,22 +7964,22 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>45812</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -7978,7 +7990,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7993,29 +8005,25 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>BBB+</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250529-ha-an-rating-withdrawal-vn-pdf.54.html</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/20250529_ha_an_rating_withdrawal-en-pdf.54.html</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8025,33 +8033,33 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
-        <v>45806</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>21/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8066,33 +8074,29 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_tpb_bao_cao_ket_qua_xhtn_21052025-pdf.53.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250529-ha-an-rating-withdrawal-vn-pdf.54.html</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating_tpb_rating_announcement_21052025-pdf.53.html</t>
+          <t>https://visrating.com/rating-results/report/20250529_ha_an_rating_withdrawal-en-pdf.54.html</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8102,22 +8106,22 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
-        <v>45798</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>21/05/2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán MB</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -8128,7 +8132,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8143,7 +8147,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8154,22 +8158,22 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_mbs_bao_cao_ket_qua_xhtn_15052025-pdf.52.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_tpb_bao_cao_ket_qua_xhtn_21052025-pdf.53.html</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating_mbs_rating_announcement_15052025-pdf.52.html</t>
+          <t>https://visrating.com/rating-results/report/visrating_tpb_rating_announcement_21052025-pdf.53.html</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8179,11 +8183,11 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
-        <v>45792</v>
+        <v>45798</v>
       </c>
     </row>
     <row r="105">
@@ -8194,7 +8198,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán UP</t>
+          <t>Công ty Cổ phần Chứng khoán MB</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -8220,7 +8224,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8231,22 +8235,22 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ups-bao-cao-ket-qua-xhtn-15052025-pdf.51.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_mbs_bao_cao_ket_qua_xhtn_15052025-pdf.52.html</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-ups-rating-announcement-15052025-pdf.51.html</t>
+          <t>https://visrating.com/rating-results/report/visrating_mbs_rating_announcement_15052025-pdf.52.html</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8256,7 +8260,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8271,7 +8275,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Chứng khoán UP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -8282,7 +8286,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8297,7 +8301,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8308,22 +8312,22 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ocb-bao-cao-ket-qua-xhtn-15052025-pdf.50.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ups-bao-cao-ket-qua-xhtn-15052025-pdf.51.html</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-ocb-rating-announcement-15052025-pdf.50.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-ups-rating-announcement-15052025-pdf.51.html</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8333,7 +8337,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8343,12 +8347,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -8359,7 +8363,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8385,22 +8389,22 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250624_vnd_rating_announcement_vn-pdf.49.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ocb-bao-cao-ket-qua-xhtn-15052025-pdf.50.html</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250624_vnd_rating_announcement_en-pdf.49.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-ocb-rating-announcement-15052025-pdf.50.html</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8410,22 +8414,22 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>08/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -8436,7 +8440,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8451,7 +8455,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8462,22 +8466,22 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-lpbank-08052025.140.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250624_vnd_rating_announcement_vn-pdf.49.html</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-lpbank-08052025.140.html</t>
+          <t>https://visrating.com/rating-results/report/20250624_vnd_rating_announcement_en-pdf.49.html</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8487,33 +8491,33 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
-        <v>45785</v>
+        <v>45791</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8528,7 +8532,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8537,16 +8541,24 @@
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-lpbank-08052025.140.html</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-lpbank-08052025.140.html</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8556,33 +8568,33 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
-        <v>45772</v>
+        <v>45785</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>25/04/2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8597,7 +8609,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8606,24 +8618,16 @@
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-bao-cao-kqxhtn-22042025vn-pdf.134.html</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-rating-announcement-22042025en-pdf.134.html</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8633,22 +8637,22 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
-        <v>45769</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>21/04/2025</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -8659,7 +8663,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8683,16 +8687,24 @@
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-bao-cao-kqxhtn-22042025vn-pdf.134.html</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/visrating-vab-rating-announcement-22042025en-pdf.134.html</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8702,28 +8714,28 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>16/03/2025</t>
+          <t>21/04/2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8743,7 +8755,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8756,12 +8768,12 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8771,22 +8783,22 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
-        <v>45732</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>16/03/2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -8797,7 +8809,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8812,7 +8824,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8821,24 +8833,16 @@
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-hut-bao-cao-ket-qua-xhtn-04122024-pdf.44.html</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-hut-rating-announcement-04122024-pdf.44.html</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8848,22 +8852,22 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
-        <v>45630</v>
+        <v>45732</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -8874,7 +8878,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8889,7 +8893,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8898,16 +8902,24 @@
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-hut-bao-cao-ket-qua-xhtn-04122024-pdf.44.html</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/vis-rating-hut-rating-announcement-04122024-pdf.44.html</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8917,28 +8929,28 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
-        <v>45625</v>
+        <v>45630</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>21/11/2024</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8958,7 +8970,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8971,12 +8983,12 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8986,22 +8998,22 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q115" s="1" t="n">
-        <v>45617</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>21/11/2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -9027,7 +9039,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -9040,12 +9052,12 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9055,22 +9067,22 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q116" s="1" t="n">
-        <v>45611</v>
+        <v>45617</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>08/11/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -9109,12 +9121,12 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9124,33 +9136,33 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q117" s="1" t="n">
-        <v>45604</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>25/10/2024</t>
+          <t>08/11/2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9165,7 +9177,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -9174,24 +9186,16 @@
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-gex-bao-cao-ket-qua-xep-hang-tin-nhiem-25102024-pdf.35.html</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-gex-rating-announcement-25102024-pdf.35.html</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9201,28 +9205,28 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q118" s="1" t="n">
-        <v>45590</v>
+        <v>45604</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>21/10/2024</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9242,7 +9246,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -9253,22 +9257,22 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-abb-bao-cao-ket-qua-xep-hang-tin-nhiem-21102024-pdf.32.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-gex-bao-cao-ket-qua-xep-hang-tin-nhiem-25102024-pdf.35.html</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-abb-rating-announcement-21102024-pdf.32.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-gex-rating-announcement-25102024-pdf.35.html</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9278,28 +9282,28 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q119" s="1" t="n">
-        <v>45586</v>
+        <v>45590</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>16/09/2024</t>
+          <t>21/10/2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9319,7 +9323,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -9330,22 +9334,22 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-phenikaa-bao-cao-ket-qua-xep-hang-tin-nhiem-16092024-pdf.31.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-abb-bao-cao-ket-qua-xep-hang-tin-nhiem-21102024-pdf.32.html</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-phenikaa-rating-announcement-16092024-pdf.31.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-abb-rating-announcement-21102024-pdf.32.html</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9355,22 +9359,22 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q120" s="1" t="n">
-        <v>45551</v>
+        <v>45586</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -9396,7 +9400,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9407,22 +9411,22 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ha-an-bao-cao-ket-qua-xep-hang-tin-nhiem-29052024-pdf.26.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-phenikaa-bao-cao-ket-qua-xep-hang-tin-nhiem-16092024-pdf.31.html</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-ha-an-rating-announcement-29052024-pdf.26.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-phenikaa-rating-announcement-16092024-pdf.31.html</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9432,28 +9436,28 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q121" s="1" t="n">
-        <v>45441</v>
+        <v>45551</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>21/05/2024</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9473,7 +9477,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9484,22 +9488,22 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-tpb-bao-cao-ket-qua-xep-hang-tin-nhiem-21052024-pdf.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ha-an-bao-cao-ket-qua-xep-hang-tin-nhiem-29052024-pdf.26.html</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-tpb-rating-announcement-21052024-pdf.25.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-ha-an-rating-announcement-29052024-pdf.26.html</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9509,22 +9513,22 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q122" s="1" t="n">
-        <v>45433</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>21/05/2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -9550,7 +9554,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9561,22 +9565,22 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ocb-bao-cao-ket-qua-xep-hang-tin-nhiem-15052024-pdf.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-tpb-bao-cao-ket-qua-xep-hang-tin-nhiem-21052024-pdf.25.html</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-ocb-rating-announcement-15052024-pdf.24.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-tpb-rating-announcement-21052024-pdf.25.html</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9586,22 +9590,22 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-10-29 10:21:44</t>
+          <t>2026-10-29 15:27:53</t>
         </is>
       </c>
       <c r="Q123" s="1" t="n">
-        <v>45427</v>
+        <v>45433</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>08/05/2024</t>
+          <t>15/05/2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -9638,35 +9642,112 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ocb-bao-cao-ket-qua-xep-hang-tin-nhiem-15052024-pdf.24.html</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/vis-rating-ocb-rating-announcement-15052024-pdf.24.html</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>VIS Rating</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:27:53</t>
+        </is>
+      </c>
+      <c r="Q124" s="1" t="n">
+        <v>45427</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>08/05/2024</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Định chế tài chính</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Xếp hạng lần đầu</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Dài hạn</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
           <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-lpbank-08052024.139.html</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>https://visrating.com/rating-results/report/rating-announcement-lpbank-08052024.139.html</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>VIS Rating</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>2026-10-29 10:21:44</t>
-        </is>
-      </c>
-      <c r="Q124" s="1" t="n">
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>VIS Rating</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:27:53</t>
+        </is>
+      </c>
+      <c r="Q125" s="1" t="n">
         <v>45420</v>
       </c>
     </row>
